--- a/reports/APEX_CHINA_W29_Weekly_Community_Report.xlsx
+++ b/reports/APEX_CHINA_W29_Weekly_Community_Report.xlsx
@@ -2,8 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rfd8ed677b98540fc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data &amp; QA" sheetId="2" r:id="R090d106b740b499a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R88c4cd63e70d4536"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -11,16 +10,133 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:comments xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:authors>
-    <x:author>tc={8C02F7B0-B0A4-B42D-CA20-3A044FBE6DE0}</x:author>
+    <x:author>tc={2BFEC025-3E66-261A-FAED-981A13487875}</x:author>
+    <x:author>tc={513AF66B-EF02-F540-2B1C-007D2705CB11}</x:author>
+    <x:author>tc={9A8D6804-8718-D298-DC1A-8C1DE5F8DAFD}</x:author>
+    <x:author>tc={9B5A567F-2ACD-B733-D8D5-C37A4D9B032D}</x:author>
+    <x:author>tc={8C330794-68DD-358B-D859-A958CD5CBD14}</x:author>
+    <x:author>tc={3FFA6BBA-F816-1440-5B48-7B6644A3A3E3}</x:author>
+    <x:author>tc={B4572395-6A51-1ED8-335E-B09728C65CE8}</x:author>
+    <x:author>tc={E6D2A9DD-0FE2-34F7-378F-9C8F004171FF}</x:author>
+    <x:author>tc={0A43A5B1-AB8A-2973-CE95-C39C6C69D891}</x:author>
   </x:authors>
   <x:commentList>
-    <x:comment ref="A2" authorId="0">
+    <x:comment ref="A5" authorId="0">
       <x:text>
         <x:r>
           <x:t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    Bilibili counts comments; Heybox counts public-search-visible posts. These units are not a platform-wide cross-platform total.</x:t>
+    W29 evidence used for this driver:
+APEX-T003 | https://www.bilibili.com/video/BV1BMjH6NEXr
+APEX-T003 | https://www.bilibili.com/video/BV14fNF6hEDV
+The narrative and sentiment were manually reviewed against the cited text; automated labels were not copied mechanically.</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="A7" authorId="1">
+      <x:text>
+        <x:r>
+          <x:t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    W29 evidence used for this driver:
+APEX-T007 | https://www.bilibili.com/video/BV1NCjx6oETt
+APEX-T007 | https://www.bilibili.com/video/BV1AxLD6pEMu
+The narrative and sentiment were manually reviewed against the cited text; automated labels were not copied mechanically.</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="A9" authorId="2">
+      <x:text>
+        <x:r>
+          <x:t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    W29 evidence used for this driver:
+APEX-T006 | https://www.bilibili.com/video/BV11VNj6KEwf
+heybox_185943073 | https://www.xiaoheihe.cn/app/bbs/link/185943073
+heybox_186154103 | https://www.xiaoheihe.cn/app/bbs/link/186154103
+The narrative and sentiment were manually reviewed against the cited text; automated labels were not copied mechanically.</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="A12" authorId="3">
+      <x:text>
+        <x:r>
+          <x:t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    W29 evidence used for this driver:
+APEX-T001 | https://www.bilibili.com/video/BV12nK66kEHn
+APEX-T001 | https://www.bilibili.com/video/BV1FHT76qEpG
+The narrative and sentiment were manually reviewed against the cited text; automated labels were not copied mechanically.</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="A14" authorId="4">
+      <x:text>
+        <x:r>
+          <x:t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    W29 evidence used for this driver:
+APEX-T002 | https://www.bilibili.com/video/BV11jMq6vEFk
+APEX-T002 | https://www.bilibili.com/video/BV13NNu6bEUa
+The narrative and sentiment were manually reviewed against the cited text; automated labels were not copied mechanically.</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="A16" authorId="5">
+      <x:text>
+        <x:r>
+          <x:t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    W29 evidence used for this driver:
+APEX-T009 | https://www.bilibili.com/video/BV17zTZ67EWq
+APEX-T009 | https://www.bilibili.com/video/BV1xcNH6SEfx
+heybox_185738105 | https://www.xiaoheihe.cn/app/bbs/link/185738105
+The narrative and sentiment were manually reviewed against the cited text; automated labels were not copied mechanically.</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="A18" authorId="6">
+      <x:text>
+        <x:r>
+          <x:t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    W29 evidence used for this driver:
+APEX-T008 | https://www.bilibili.com/video/BV1D9Nn6sEwa
+APEX-T008 | https://www.bilibili.com/video/BV15VMw6DEZe
+The narrative and sentiment were manually reviewed against the cited text; automated labels were not copied mechanically.</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="A20" authorId="7">
+      <x:text>
+        <x:r>
+          <x:t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    W29 evidence used for this driver:
+APEX-T010 | https://www.bilibili.com/video/BV11pTv6fEt9
+APEX-T010 | https://www.bilibili.com/video/BV1QSNu6tEpt
+The narrative and sentiment were manually reviewed against the cited text; automated labels were not copied mechanically.</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="A2" authorId="8">
+      <x:text>
+        <x:r>
+          <x:t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Coverage: 2026-07-13—2026-07-19 (Asia/Shanghai).
+Bilibili counts visible comments; Heybox counts public-search-visible post cards. The units are incomparable and are not added as a platform-wide total.
+Eight independent drivers were retained after evidence review; vague, duplicative or misclassified texts were excluded from the narrative.
+This bounded sample is not qualified for platform-wide statistical reporting.</x:t>
         </x:r>
       </x:text>
     </x:comment>
@@ -34,15 +150,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <x:numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <x:numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <x:numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <x:numFmt numFmtId="200" formatCode="0.0%"/>
-    <x:numFmt numFmtId="201" formatCode="0.000"/>
   </x:numFmts>
-  <x:fonts count="57">
+  <x:fonts count="38">
     <x:font>
       <x:sz val="11"/>
       <x:color theme="1"/>
@@ -229,149 +343,36 @@
     </x:font>
     <x:font>
       <x:b/>
-      <x:i/>
-      <x:sz val="6"/>
+      <x:sz val="11"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Source Sans Pro"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
       <x:color rgb="FF434343"/>
       <x:name val="Source Sans Pro"/>
     </x:font>
     <x:font>
-      <x:b/>
-      <x:sz val="6"/>
+      <x:i/>
+      <x:sz val="11"/>
       <x:color rgb="FF434343"/>
       <x:name val="Source Sans Pro"/>
     </x:font>
     <x:font>
       <x:b/>
-      <x:sz val="9"/>
-      <x:color rgb="FF434343"/>
+      <x:sz val="11"/>
+      <x:color rgb="FF008000"/>
       <x:name val="Source Sans Pro"/>
     </x:font>
     <x:font>
-      <x:sz val="11"/>
-      <x:color theme="1"/>
-      <x:name val="宋体"/>
-    </x:font>
-    <x:font>
-      <x:i/>
-      <x:sz val="11"/>
-      <x:color theme="1"/>
-      <x:name val="宋体"/>
-    </x:font>
-    <x:font>
-      <x:i/>
-      <x:sz val="6"/>
-      <x:color theme="1"/>
-      <x:name val="宋体"/>
-    </x:font>
-    <x:font>
-      <x:i/>
-      <x:sz val="6"/>
-      <x:color theme="1"/>
-      <x:name val="Source Sans Pro"/>
-    </x:font>
-    <x:font>
-      <x:i/>
-      <x:sz val="6"/>
-      <x:color rgb="FF434343"/>
-      <x:name val="Source Sans Pro"/>
-    </x:font>
-    <x:font>
       <x:b/>
       <x:sz val="11"/>
-      <x:color rgb="FFFF0000"/>
-      <x:name val="宋体"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="11"/>
-      <x:color rgb="FFFF0000"/>
-      <x:name val="宋体"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="11"/>
-      <x:color theme="1"/>
-      <x:name val="宋体"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="8"/>
-      <x:color rgb="FFFF0000"/>
-      <x:name val="宋体"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="8"/>
-      <x:color theme="1"/>
-      <x:name val="宋体"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="8"/>
       <x:color rgb="FFFF0000"/>
       <x:name val="Source Sans Pro"/>
     </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="8"/>
-      <x:color theme="1"/>
-      <x:name val="Source Sans Pro"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="9"/>
-      <x:color theme="1"/>
-      <x:name val="宋体"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="9"/>
-      <x:color theme="1"/>
-      <x:name val="Source Sans Pro"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="8"/>
-      <x:color rgb="FF008000"/>
-      <x:name val="Source Sans Pro"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="8"/>
-      <x:color rgb="FF434343"/>
-      <x:name val="Source Sans Pro"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="15"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Aptos Display"/>
-    </x:font>
-    <x:font>
-      <x:i/>
-      <x:sz val="9"/>
-      <x:color rgb="FF34495E"/>
-      <x:name val="Aptos"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="11"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Aptos"/>
-    </x:font>
-    <x:font>
-      <x:sz val="9"/>
-      <x:color rgb="FF273444"/>
-      <x:name val="Aptos"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="11"/>
-      <x:color rgb="FF244B2A"/>
-      <x:name val="Aptos"/>
-    </x:font>
   </x:fonts>
-  <x:fills count="40">
+  <x:fills count="37">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -545,31 +546,16 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFFFFF"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF18324A"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFE8F0F7"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF2F5D7C"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFEAF3EA"/>
+        <x:fgColor rgb="FF85200C"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9D9D9"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
-  <x:borders count="26">
+  <x:borders count="20">
     <x:border/>
     <x:border>
       <x:left style="medium">
@@ -713,87 +699,41 @@
       </x:bottom>
     </x:border>
     <x:border>
-      <x:right style="medium">
-        <x:color rgb="FF999999"/>
-      </x:right>
+      <x:left style="medium">
+        <x:color rgb="FF999999"/>
+      </x:left>
+      <x:top style="medium">
+        <x:color rgb="FF999999"/>
+      </x:top>
+      <x:bottom style="none"/>
     </x:border>
     <x:border>
-      <x:left style="thin">
-        <x:color rgb="FF9FB5C4"/>
+      <x:right style="medium">
+        <x:color rgb="FF999999"/>
+      </x:right>
+      <x:top style="medium">
+        <x:color rgb="FF999999"/>
+      </x:top>
+      <x:bottom style="none"/>
+    </x:border>
+    <x:border>
+      <x:left style="medium">
+        <x:color rgb="FF999999"/>
       </x:left>
-      <x:top style="thin">
-        <x:color rgb="FF9FB5C4"/>
+      <x:right style="medium">
+        <x:color rgb="FF999999"/>
+      </x:right>
+      <x:top style="medium">
+        <x:color rgb="FF999999"/>
       </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="FF9FB5C4"/>
+      <x:bottom style="medium">
+        <x:color rgb="FF999999"/>
       </x:bottom>
     </x:border>
     <x:border>
-      <x:top style="thin">
-        <x:color rgb="FF9FB5C4"/>
-      </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="FF9FB5C4"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
-      <x:right style="thin">
-        <x:color rgb="FF9FB5C4"/>
+      <x:right style="medium">
+        <x:color rgb="FF999999"/>
       </x:right>
-      <x:top style="thin">
-        <x:color rgb="FF9FB5C4"/>
-      </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="FF9FB5C4"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
-      <x:bottom style="thin">
-        <x:color rgb="FFD7E0E7"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
-      <x:top style="thin">
-        <x:color rgb="FFD7E0E7"/>
-      </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="FFD7E0E7"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
-      <x:top style="thin">
-        <x:color rgb="FFD7E0E7"/>
-      </x:top>
-    </x:border>
-    <x:border>
-      <x:left style="thin">
-        <x:color rgb="FF9BB89F"/>
-      </x:left>
-      <x:top style="thin">
-        <x:color rgb="FF9BB89F"/>
-      </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="FF9BB89F"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
-      <x:top style="thin">
-        <x:color rgb="FF9BB89F"/>
-      </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="FF9BB89F"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
-      <x:right style="thin">
-        <x:color rgb="FF9BB89F"/>
-      </x:right>
-      <x:top style="thin">
-        <x:color rgb="FF9BB89F"/>
-      </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="FF9BB89F"/>
-      </x:bottom>
     </x:border>
   </x:borders>
   <x:cellStyleXfs count="49">
@@ -945,7 +885,7 @@
       <x:alignment vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="119">
+  <x:cellXfs count="89">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:alignment vertical="center"/>
     </x:xf>
@@ -1000,308 +940,218 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
       <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="35" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="33" fillId="35" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="34" fillId="35" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="35" fillId="35" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="35" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="36" fillId="35" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="37" fillId="35" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="38" fillId="35" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="39" fillId="35" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="40" fillId="35" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="35" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="35" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="41" fillId="35" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="26" fillId="35" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="42" fillId="35" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="43" fillId="35" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="44" fillId="35" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="45" fillId="35" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="46" fillId="35" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="47" fillId="35" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="47" fillId="35" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="47" fillId="35" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="26" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="43" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="48" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="49" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="35" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="35" fillId="35" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="35" fillId="35" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="36" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="37" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="38" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="39" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="40" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="40" fillId="35" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="40" fillId="35" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="45" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="47" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="47" fillId="35" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="47" fillId="35" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="47" fillId="35" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="top" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="50" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="top" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="51" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="top" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="46" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="top" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="50" fillId="35" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="top" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="46" fillId="35" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="33" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="33" fillId="35" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="33" fillId="35" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="33" fillId="35" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="33" fillId="35" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="33" fillId="35" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="35" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="35" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="33" fillId="35" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="33" fillId="35" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="33" fillId="35" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="33" fillId="35" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="33" fillId="35" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="33" fillId="35" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="33" fillId="35" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="52" fillId="36" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="52" fillId="36" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="37" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="53" fillId="37" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="53" fillId="37" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="34" fillId="36" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="34" fillId="36" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="34" fillId="36" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="38" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="54" fillId="38" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="54" fillId="38" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="54" fillId="38" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="54" fillId="38" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="55" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="55" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="55" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="39" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="56" fillId="39" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="56" fillId="39" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="56" fillId="39" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="56" fillId="39" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="55" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="55" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="55" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="201" fontId="55" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="201" fontId="55" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="201" fontId="55" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="56" fillId="39" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="54" fillId="38" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="34" fillId="36" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="34" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="34" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="54" fillId="38" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="34" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="34" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="35" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="35" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="54" fillId="38" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="35" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="35" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="35" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="35" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="55" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="35" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="35" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="36" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="36" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="36" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="200" fontId="55" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="36" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="201" fontId="55" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="36" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="36" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="34" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="34" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="34" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="55" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="34" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="200" fontId="55" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="34" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="34" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="37" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="37" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="37" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="201" fontId="55" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="37" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="55" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="55" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="201" fontId="55" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="56" fillId="39" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="56" fillId="39" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="56" fillId="39" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
+    <x:xf numFmtId="0" fontId="37" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="37" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="49">
@@ -1540,7 +1390,7 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <xltc:personList xmlns:xltc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <xltc:person displayName="User" id="{CD203006-1D62-4DA4-9446-416593376679}"/>
+  <xltc:person displayName="choco" id="{72F5DFA6-FD2E-4557-A292-1F8CFA0D0972}"/>
 </xltc:personList>
 </file>
 
@@ -1602,30 +1452,12 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:lumOff val="17500"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr"/>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="2700000" scaled="0"/>
-        </a:gradFill>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr"/>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr"/>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="2700000" scaled="0"/>
-        </a:gradFill>
+        <a:solidFill>
+          <a:schemeClr val="dk1"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="accent1"/>
+        </a:solidFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="12700">
@@ -1690,7 +1522,7 @@
             <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -1725,8 +1557,61 @@
 
 <file path=xl/threadedcomments/threadedcomment.xml><?xml version="1.0" encoding="utf-8"?>
 <xltc:ThreadedComments xmlns:xltc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <xltc:threadedComment ref="A2" dT="2026-07-23T07:04:54.708" personId="{CD203006-1D62-4DA4-9446-416593376679}" id="{8C02F7B0-B0A4-B42D-CA20-3A044FBE6DE0}">
-    <xltc:text>Bilibili counts comments; Heybox counts public-search-visible posts. These units are not a platform-wide cross-platform total.</xltc:text>
+  <xltc:threadedComment ref="A5" dT="2026-07-28T02:56:21.077" personId="{72F5DFA6-FD2E-4557-A292-1F8CFA0D0972}" id="{2BFEC025-3E66-261A-FAED-981A13487875}">
+    <xltc:text>W29 evidence used for this driver:
+APEX-T003 | https://www.bilibili.com/video/BV1BMjH6NEXr
+APEX-T003 | https://www.bilibili.com/video/BV14fNF6hEDV
+The narrative and sentiment were manually reviewed against the cited text; automated labels were not copied mechanically.</xltc:text>
+  </xltc:threadedComment>
+  <xltc:threadedComment ref="A7" dT="2026-07-28T02:56:21.077" personId="{72F5DFA6-FD2E-4557-A292-1F8CFA0D0972}" id="{513AF66B-EF02-F540-2B1C-007D2705CB11}">
+    <xltc:text>W29 evidence used for this driver:
+APEX-T007 | https://www.bilibili.com/video/BV1NCjx6oETt
+APEX-T007 | https://www.bilibili.com/video/BV1AxLD6pEMu
+The narrative and sentiment were manually reviewed against the cited text; automated labels were not copied mechanically.</xltc:text>
+  </xltc:threadedComment>
+  <xltc:threadedComment ref="A9" dT="2026-07-28T02:56:21.077" personId="{72F5DFA6-FD2E-4557-A292-1F8CFA0D0972}" id="{9A8D6804-8718-D298-DC1A-8C1DE5F8DAFD}">
+    <xltc:text>W29 evidence used for this driver:
+APEX-T006 | https://www.bilibili.com/video/BV11VNj6KEwf
+heybox_185943073 | https://www.xiaoheihe.cn/app/bbs/link/185943073
+heybox_186154103 | https://www.xiaoheihe.cn/app/bbs/link/186154103
+The narrative and sentiment were manually reviewed against the cited text; automated labels were not copied mechanically.</xltc:text>
+  </xltc:threadedComment>
+  <xltc:threadedComment ref="A12" dT="2026-07-28T02:56:21.077" personId="{72F5DFA6-FD2E-4557-A292-1F8CFA0D0972}" id="{9B5A567F-2ACD-B733-D8D5-C37A4D9B032D}">
+    <xltc:text>W29 evidence used for this driver:
+APEX-T001 | https://www.bilibili.com/video/BV12nK66kEHn
+APEX-T001 | https://www.bilibili.com/video/BV1FHT76qEpG
+The narrative and sentiment were manually reviewed against the cited text; automated labels were not copied mechanically.</xltc:text>
+  </xltc:threadedComment>
+  <xltc:threadedComment ref="A14" dT="2026-07-28T02:56:21.077" personId="{72F5DFA6-FD2E-4557-A292-1F8CFA0D0972}" id="{8C330794-68DD-358B-D859-A958CD5CBD14}">
+    <xltc:text>W29 evidence used for this driver:
+APEX-T002 | https://www.bilibili.com/video/BV11jMq6vEFk
+APEX-T002 | https://www.bilibili.com/video/BV13NNu6bEUa
+The narrative and sentiment were manually reviewed against the cited text; automated labels were not copied mechanically.</xltc:text>
+  </xltc:threadedComment>
+  <xltc:threadedComment ref="A16" dT="2026-07-28T02:56:21.077" personId="{72F5DFA6-FD2E-4557-A292-1F8CFA0D0972}" id="{3FFA6BBA-F816-1440-5B48-7B6644A3A3E3}">
+    <xltc:text>W29 evidence used for this driver:
+APEX-T009 | https://www.bilibili.com/video/BV17zTZ67EWq
+APEX-T009 | https://www.bilibili.com/video/BV1xcNH6SEfx
+heybox_185738105 | https://www.xiaoheihe.cn/app/bbs/link/185738105
+The narrative and sentiment were manually reviewed against the cited text; automated labels were not copied mechanically.</xltc:text>
+  </xltc:threadedComment>
+  <xltc:threadedComment ref="A18" dT="2026-07-28T02:56:21.077" personId="{72F5DFA6-FD2E-4557-A292-1F8CFA0D0972}" id="{B4572395-6A51-1ED8-335E-B09728C65CE8}">
+    <xltc:text>W29 evidence used for this driver:
+APEX-T008 | https://www.bilibili.com/video/BV1D9Nn6sEwa
+APEX-T008 | https://www.bilibili.com/video/BV15VMw6DEZe
+The narrative and sentiment were manually reviewed against the cited text; automated labels were not copied mechanically.</xltc:text>
+  </xltc:threadedComment>
+  <xltc:threadedComment ref="A20" dT="2026-07-28T02:56:21.077" personId="{72F5DFA6-FD2E-4557-A292-1F8CFA0D0972}" id="{E6D2A9DD-0FE2-34F7-378F-9C8F004171FF}">
+    <xltc:text>W29 evidence used for this driver:
+APEX-T010 | https://www.bilibili.com/video/BV11pTv6fEt9
+APEX-T010 | https://www.bilibili.com/video/BV1QSNu6tEpt
+The narrative and sentiment were manually reviewed against the cited text; automated labels were not copied mechanically.</xltc:text>
+  </xltc:threadedComment>
+  <xltc:threadedComment ref="A2" dT="2026-07-28T02:56:21.077" personId="{72F5DFA6-FD2E-4557-A292-1F8CFA0D0972}" id="{0A43A5B1-AB8A-2973-CE95-C39C6C69D891}">
+    <xltc:text>Coverage: 2026-07-13—2026-07-19 (Asia/Shanghai).
+Bilibili counts visible comments; Heybox counts public-search-visible post cards. The units are incomparable and are not added as a platform-wide total.
+Eight independent drivers were retained after evidence review; vague, duplicative or misclassified texts were excluded from the narrative.
+This bounded sample is not qualified for platform-wide statistical reporting.</xltc:text>
   </xltc:threadedComment>
 </xltc:ThreadedComments>
 </file>
@@ -1737,6 +1622,9 @@
   <x:cols>
     <x:col min="1" max="1" width="41.50893020629883" customWidth="1"/>
     <x:col min="2" max="2" width="12.642857551574707" customWidth="1"/>
+    <x:col min="3" max="3" width="2.200000047683716" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="41.50893020629883" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="12.642857551574707" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" customHeight="1">
@@ -1744,164 +1632,244 @@
         <x:v>CHINA · W29</x:v>
       </x:c>
       <x:c r="B1" s="2"/>
-    </x:row>
-    <x:row r="2" ht="19.75" customHeight="1">
+      <x:c r="D1" s="41" t="str">
+        <x:v>中国 · W29</x:v>
+      </x:c>
+      <x:c r="E1" s="42"/>
+    </x:row>
+    <x:row r="2" ht="36" customHeight="1">
       <x:c r="A2" s="3" t="str">
-        <x:v>Bounded sample: 186 Bilibili comments (105 mapped) | 12 Heybox search-visible posts (10 mapped) | 2026-07-13—2026-07-19</x:v>
+        <x:v>Weekly conversations: 186 Bilibili comments; 12 Heybox posts | Bounded samples with incomparable units</x:v>
       </x:c>
       <x:c r="B2" s="4"/>
+      <x:c r="D2" s="47" t="str">
+        <x:v>每周讨论量：186条B站评论；12篇小黑盒帖子｜有限样本，单位不可比</x:v>
+      </x:c>
+      <x:c r="E2" s="48"/>
     </x:row>
     <x:row r="3" ht="17.549999237060547">
       <x:c r="A3" s="5" t="str">
-        <x:v>TOPIC / DRIVER</x:v>
+        <x:v>TOPIC/DRIVER</x:v>
       </x:c>
       <x:c r="B3" s="6" t="str">
-        <x:v>MODEL SENTIMENT</x:v>
+        <x:v>SENTIMENT</x:v>
+      </x:c>
+      <x:c r="D3" s="53" t="str">
+        <x:v>话题/驱动因素</x:v>
+      </x:c>
+      <x:c r="E3" s="53" t="str">
+        <x:v>情绪</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18.299999237060547" customHeight="1">
       <x:c r="A4" s="7" t="str">
-        <x:v>Season Update Friction</x:v>
-      </x:c>
-      <x:c r="B4" s="64" t="str">
-        <x:v>Negative</x:v>
+        <x:v>Creator Performance Interest</x:v>
+      </x:c>
+      <x:c r="B4" s="18" t="str">
+        <x:v>Positive</x:v>
+      </x:c>
+      <x:c r="D4" s="58" t="str">
+        <x:v>主播竞技表现关注</x:v>
+      </x:c>
+      <x:c r="E4" s="74" t="str">
+        <x:v>正向</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="102.75">
       <x:c r="A5" s="9" t="str">
-        <x:v>Players discussed update reliability, driver conflicts and changes that increasingly favor experienced users. Repeated technical friction and concerns about reduced accessibility outweighed positive reactions in this bounded Bilibili sample.</x:v>
+        <x:v>Viewers highlighted professional-level recoil control, smooth controller execution and specific creator techniques. The visible skill ceiling encouraged hardware and settings questions and sustained interest in performance-led content.</x:v>
       </x:c>
       <x:c r="B5" s="8"/>
+      <x:c r="D5" s="63" t="str">
+        <x:v>观众关注职业级压枪、流畅的手柄操作和具体主播技巧。可见的技术上限带动了硬件与设置提问，也持续强化了对竞技表现型内容的兴趣。</x:v>
+      </x:c>
+      <x:c r="E5" s="75"/>
     </x:row>
     <x:row r="6" ht="42.5" customHeight="1">
       <x:c r="A6" s="7" t="str">
-        <x:v>Ranked Matchmaking Pressure</x:v>
-      </x:c>
-      <x:c r="B6" s="64" t="str">
-        <x:v>Negative</x:v>
+        <x:v>Settings Help Requests</x:v>
+      </x:c>
+      <x:c r="B6" s="19" t="str">
+        <x:v>Neutral</x:v>
+      </x:c>
+      <x:c r="D6" s="58" t="str">
+        <x:v>设置求助需求</x:v>
+      </x:c>
+      <x:c r="E6" s="80" t="str">
+        <x:v>中性</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="129.75">
       <x:c r="A7" s="9" t="str">
-        <x:v>Ranked players described forced solo queue, weak team coordination and uneven lobbies as major pressure points. Positive progression stories remained visible, but frustration was slightly more common in the mapped sample.</x:v>
+        <x:v>Players sought practical help with DSE settings, forced resolution resets and recoil habits. The discussion centered on troubleshooting and learning rather than product judgment, so it did not support a directional sentiment conclusion.</x:v>
       </x:c>
       <x:c r="B7" s="10"/>
+      <x:c r="D7" s="63" t="str">
+        <x:v>玩家集中求助DSE设置、分辨率被强制重置和压枪习惯等问题。讨论核心是排障与学习，而非对产品作价值判断，因此不支持明确的情绪方向结论。</x:v>
+      </x:c>
+      <x:c r="E7" s="81"/>
     </x:row>
     <x:row r="8" ht="29.5" customHeight="1">
       <x:c r="A8" s="7" t="str">
-        <x:v>Cyberpunk Collaboration</x:v>
-      </x:c>
-      <x:c r="B8" s="64" t="str">
+        <x:v>Cyberpunk Reward Friction</x:v>
+      </x:c>
+      <x:c r="B8" s="20" t="str">
         <x:v>Negative</x:v>
+      </x:c>
+      <x:c r="D8" s="58" t="str">
+        <x:v>《赛博朋克》奖励阻力</x:v>
+      </x:c>
+      <x:c r="E8" s="87" t="str">
+        <x:v>负向</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="175.75">
       <x:c r="A9" s="12" t="str">
-        <x:v>The Cyberpunk collaboration drove the strongest cross-platform attention through reward guides, pricing questions and launch updates. Bilibili reactions were notably negative, while Heybox posts concentrated on claiming rewards and purchase planning.</x:v>
+        <x:v>The Cyberpunk launch generated cross-platform attention around free rewards, refresh timing and total purchase cost. Bilibili reactions criticized the crossover fit, while Heybox questions showed uncertainty that could delay claiming or spending decisions.</x:v>
       </x:c>
       <x:c r="B9" s="11"/>
+      <x:c r="D9" s="67" t="str">
+        <x:v>《赛博朋克》联动上线后，两平台关注点集中在免费奖励、刷新时间与完整购买成本。B站评论质疑联动契合度，小黑盒提问则反映信息不确定，可能延迟领取或消费决策。</x:v>
+      </x:c>
+      <x:c r="E9" s="87"/>
     </x:row>
     <x:row r="10" ht="17.549999237060547">
       <x:c r="A10" s="9"/>
       <x:c r="B10" s="11"/>
+      <x:c r="D10" s="68"/>
+      <x:c r="E10" s="88"/>
     </x:row>
     <x:row r="11" ht="42.5" customHeight="1">
       <x:c r="A11" s="7" t="str">
-        <x:v>Creator Performance Interest</x:v>
-      </x:c>
-      <x:c r="B11" s="60" t="str">
-        <x:v>Positive</x:v>
+        <x:v>Ranked Solo-Queue Coordination</x:v>
+      </x:c>
+      <x:c r="B11" s="20" t="str">
+        <x:v>Negative</x:v>
+      </x:c>
+      <x:c r="D11" s="58" t="str">
+        <x:v>排位单排协同</x:v>
+      </x:c>
+      <x:c r="E11" s="87" t="str">
+        <x:v>负向</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="83.75">
       <x:c r="A12" s="9" t="str">
-        <x:v>Viewers showed positive interest in streamer technique, controller smoothness and professional play. Questions about hardware and execution helped sustain engagement, with favorable reactions exceeding negative discussion in the sample.</x:v>
+        <x:v>Diamond-and-above players said forced solo queue reduced their ability to coordinate pushes and protect gains. Without reliable teammate follow-through, cautious play became more attractive and ranked progression felt less rewarding.</x:v>
       </x:c>
       <x:c r="B12" s="8"/>
+      <x:c r="D12" s="63" t="str">
+        <x:v>钻石及以上玩家认为强制单排削弱了推进协同和保分能力。队友无法稳定跟进时，保守打法更具吸引力，排位进度的回报感也随之下降。</x:v>
+      </x:c>
+      <x:c r="E12" s="81"/>
     </x:row>
     <x:row r="13" ht="42.5" customHeight="1">
       <x:c r="A13" s="7" t="str">
-        <x:v>Cosmetic Experience Friction</x:v>
-      </x:c>
-      <x:c r="B13" s="60" t="str">
-        <x:v>Positive</x:v>
+        <x:v>Update Reliability Friction</x:v>
+      </x:c>
+      <x:c r="B13" s="20" t="str">
+        <x:v>Negative</x:v>
+      </x:c>
+      <x:c r="D13" s="58" t="str">
+        <x:v>更新可靠性阻力</x:v>
+      </x:c>
+      <x:c r="E13" s="87" t="str">
+        <x:v>负向</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="111.75">
       <x:c r="A14" s="13" t="str">
-        <x:v>Cosmetic and interface conversations mixed appreciation with complaints about latency, missing match history and anti-cheat quality. Positive model labels led narrowly, but the evidence remains mixed and sample-limited.</x:v>
+        <x:v>Players linked driver conflicts, recurring update problems and reduced accessibility for newcomers to a broader decline in reliability. Repeated friction outweighed isolated positive tactics discussion and weakened willingness to recommend returning.</x:v>
       </x:c>
       <x:c r="B14" s="11"/>
+      <x:c r="D14" s="63" t="str">
+        <x:v>玩家将驱动冲突、反复出现的更新问题和新手门槛上升联系到整体可靠性下降。持续摩擦压过了零散的正向技巧讨论，也削弱了推荐他人回归的意愿。</x:v>
+      </x:c>
+      <x:c r="E14" s="81"/>
     </x:row>
     <x:row r="15" ht="42.5" customHeight="1">
       <x:c r="A15" s="7" t="str">
-        <x:v>Ranked Version Discussion</x:v>
-      </x:c>
-      <x:c r="B15" s="60" t="str">
-        <x:v>Positive</x:v>
+        <x:v>Core-System Trust</x:v>
+      </x:c>
+      <x:c r="B15" s="20" t="str">
+        <x:v>Negative</x:v>
+      </x:c>
+      <x:c r="D15" s="58" t="str">
+        <x:v>基础系统信任</x:v>
+      </x:c>
+      <x:c r="E15" s="87" t="str">
+        <x:v>负向</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="157.75">
       <x:c r="A16" s="9" t="str">
-        <x:v>Version, Ranked and tournament comments leaned positive around workable tactics and mechanical control. A Heybox cheating complaint added risk context, but it represents one search-visible post rather than platform-wide prevalence.</x:v>
+        <x:v>High latency, missing match-history functions and frustration with both cheating and false bans were discussed together as neglected basics. When several core systems felt unreliable, confidence extended beyond one match and affected the game’s overall credibility.</x:v>
       </x:c>
       <x:c r="B16" s="11"/>
+      <x:c r="D16" s="63" t="str">
+        <x:v>高延迟、对局记录缺失，以及外挂与误封并存的抱怨，被玩家归为长期未完善的基础问题。多个核心系统同时缺乏可靠性时，不满会从单局体验扩展到对游戏整体可信度的判断。</x:v>
+      </x:c>
+      <x:c r="E16" s="88"/>
     </x:row>
     <x:row r="17" ht="18.299999237060547" customHeight="1">
       <x:c r="A17" s="7" t="str">
-        <x:v>Legend Ability Balance</x:v>
-      </x:c>
-      <x:c r="B17" s="64" t="str">
-        <x:v>Negative</x:v>
+        <x:v>Pathfinder Mobility Ceiling</x:v>
+      </x:c>
+      <x:c r="B17" s="19" t="str">
+        <x:v>Neutral</x:v>
+      </x:c>
+      <x:c r="D17" s="58" t="str">
+        <x:v>探路者机动上限</x:v>
+      </x:c>
+      <x:c r="E17" s="80" t="str">
+        <x:v>中性</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="148.75">
       <x:c r="A18" s="9" t="str">
-        <x:v>Players compared ultimate designs, controller accessories and potential ability changes. Negative reactions formed the largest single sentiment group, although positive and neutral responses together prevented a clear consensus.</x:v>
+        <x:v>Players agreed that Pathfinder’s mobility and double-ultimate efficiency could create a high ceiling, while also comparing simpler movement alternatives. Recognition of strength was balanced by execution demands and requests for other Legends.</x:v>
       </x:c>
       <x:c r="B18" s="10"/>
+      <x:c r="D18" s="63" t="str">
+        <x:v>玩家认可探路者机动性和双大招效率带来的高上限，同时也将其与更易上手的机动角色比较。强度认可受到操作门槛和其他传奇加强诉求的平衡，整体保持中性。</x:v>
+      </x:c>
+      <x:c r="E18" s="81"/>
     </x:row>
     <x:row r="19" ht="29.5" customHeight="1">
       <x:c r="A19" s="7" t="str">
-        <x:v>Mobility Strength Debate</x:v>
-      </x:c>
-      <x:c r="B19" s="62" t="str">
-        <x:v>Neutral</x:v>
+        <x:v>Tournament Fairness Criteria</x:v>
+      </x:c>
+      <x:c r="B19" s="20" t="str">
+        <x:v>Negative</x:v>
+      </x:c>
+      <x:c r="D19" s="58" t="str">
+        <x:v>赛事公平标准</x:v>
+      </x:c>
+      <x:c r="E19" s="87" t="str">
+        <x:v>负向</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="148.75">
       <x:c r="A20" s="9" t="str">
-        <x:v>Discussion of mobile Legends emphasized strong movement ceilings and efficient double-ultimate play. Positive and neutral model labels were evenly split, suggesting interest without a dominant risk signal.</x:v>
+        <x:v>Tournament viewers questioned roster limits and inconsistent MVP criteria across events. When rules appeared to shift between leadership, data and input narratives, award legitimacy and competitive fairness became harder to trust.</x:v>
       </x:c>
       <x:c r="B20" s="11"/>
-    </x:row>
-    <x:row r="21" ht="29.5" customHeight="1">
-      <x:c r="A21" s="21" t="str">
-        <x:v>Settings Help Requests</x:v>
-      </x:c>
-      <x:c r="B21" s="68" t="str">
-        <x:v>Neutral</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" ht="148.75" customHeight="1">
-      <x:c r="A22" s="27" t="str">
-        <x:v>Players sought help with display resolution, controller configuration and unclear creator drama. All mapped Bilibili comments were model-labeled neutral, indicating practical information needs rather than a strong sentiment shift.</x:v>
-      </x:c>
-      <x:c r="B22" s="39"/>
-    </x:row>
-    <x:row r="23" ht="29.5" customHeight="1">
-      <x:c r="A23" s="47" t="str">
-        <x:v>Tournament Fairness Debate</x:v>
-      </x:c>
-      <x:c r="B23" s="69" t="str">
-        <x:v>Negative</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" ht="148.75" customHeight="1">
-      <x:c r="A24" s="54" t="str">
-        <x:v>Tournament viewers questioned roster rules, award consistency and competitive fairness. Two-thirds of mapped comments were model-labeled negative, making this a review priority despite the small six-comment sample.</x:v>
-      </x:c>
-      <x:c r="B24" s="39"/>
+      <x:c r="D20" s="63" t="str">
+        <x:v>赛事观众质疑队伍限制与历届MVP标准是否一致。当评选依据在指挥能力、数据表现和输入方式叙事之间摇摆时，奖项公信力和竞技公平性更难获得信任。</x:v>
+      </x:c>
+      <x:c r="E20" s="88"/>
+    </x:row>
+    <x:row r="21" ht="17.549999237060547">
+      <x:c r="A21" s="14"/>
+      <x:c r="B21" s="15"/>
+      <x:c r="D21"/>
+      <x:c r="E21"/>
+    </x:row>
+    <x:row r="22" ht="17.549999237060547">
+      <x:c r="A22" s="16"/>
+      <x:c r="B22" s="17"/>
+      <x:c r="D22"/>
+      <x:c r="E22"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -1914,625 +1882,19 @@
     <x:mergeCell ref="B15:B16"/>
     <x:mergeCell ref="B17:B18"/>
     <x:mergeCell ref="B19:B20"/>
-    <x:mergeCell ref="B21:B22"/>
-    <x:mergeCell ref="B23:B24"/>
     <x:mergeCell ref="A2:B2"/>
+    <x:mergeCell ref="D1:E1"/>
+    <x:mergeCell ref="D2:E2"/>
+    <x:mergeCell ref="E4:E5"/>
+    <x:mergeCell ref="E6:E7"/>
+    <x:mergeCell ref="E8:E10"/>
+    <x:mergeCell ref="E11:E12"/>
+    <x:mergeCell ref="E13:E14"/>
+    <x:mergeCell ref="E15:E16"/>
+    <x:mergeCell ref="E17:E18"/>
+    <x:mergeCell ref="E19:E20"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R269f7846f1334776"/>
-</x:worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="28" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="17" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="17" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="24" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="48" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="12" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="12" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="16" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="28" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="28" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1" ht="28" customHeight="1">
-      <x:c r="A1" s="72" t="str">
-        <x:v>W29 SOURCE DATA AND QUALITY CHECKS</x:v>
-      </x:c>
-      <x:c r="B1" s="72"/>
-      <x:c r="C1" s="72"/>
-      <x:c r="D1" s="72"/>
-      <x:c r="E1" s="72"/>
-      <x:c r="F1" s="72"/>
-      <x:c r="G1" s="72"/>
-      <x:c r="H1" s="72"/>
-      <x:c r="I1" s="72"/>
-      <x:c r="J1" s="72"/>
-    </x:row>
-    <x:row r="2" ht="34" customHeight="1">
-      <x:c r="A2" s="75" t="str">
-        <x:v>Model-only exploratory output. Bilibili comments and Heybox visible posts have different units and must not be added as a platform-wide total.</x:v>
-      </x:c>
-      <x:c r="B2" s="75"/>
-      <x:c r="C2" s="75"/>
-      <x:c r="D2" s="75"/>
-      <x:c r="E2" s="75"/>
-      <x:c r="F2" s="75"/>
-      <x:c r="G2" s="75"/>
-      <x:c r="H2" s="75"/>
-      <x:c r="I2" s="75"/>
-      <x:c r="J2" s="75"/>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="100" t="str">
-        <x:v>Topic</x:v>
-      </x:c>
-      <x:c r="B4" s="101" t="str">
-        <x:v>Bilibili mapped comments</x:v>
-      </x:c>
-      <x:c r="C4" s="101" t="str">
-        <x:v>Heybox visible posts</x:v>
-      </x:c>
-      <x:c r="D4" s="101" t="str">
-        <x:v>Positive</x:v>
-      </x:c>
-      <x:c r="E4" s="101" t="str">
-        <x:v>Neutral</x:v>
-      </x:c>
-      <x:c r="F4" s="101" t="str">
-        <x:v>Negative</x:v>
-      </x:c>
-      <x:c r="G4" s="101" t="str">
-        <x:v>Average score</x:v>
-      </x:c>
-      <x:c r="H4" s="101" t="str">
-        <x:v>Model sentiment</x:v>
-      </x:c>
-      <x:c r="I4" s="101" t="str">
-        <x:v>Bilibili source</x:v>
-      </x:c>
-      <x:c r="J4" s="102" t="str">
-        <x:v>Heybox source</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" s="103" t="str">
-        <x:v>Season Update Friction</x:v>
-      </x:c>
-      <x:c r="B5" s="103" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C5" s="103" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D5" s="104" t="n">
-        <x:v>0.3</x:v>
-      </x:c>
-      <x:c r="E5" s="104" t="n">
-        <x:v>0.25</x:v>
-      </x:c>
-      <x:c r="F5" s="104" t="n">
-        <x:v>0.45</x:v>
-      </x:c>
-      <x:c r="G5" s="105" t="n">
-        <x:v>0.455451</x:v>
-      </x:c>
-      <x:c r="H5" s="103" t="str">
-        <x:v>Negative</x:v>
-      </x:c>
-      <x:c r="I5" s="103" t="str">
-        <x:v>https://www.bilibili.com</x:v>
-      </x:c>
-      <x:c r="J5" s="103" t="str">
-        <x:v>https://www.xiaoheihe.cn</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="106" t="str">
-        <x:v>Ranked Matchmaking Pressure</x:v>
-      </x:c>
-      <x:c r="B6" s="106" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C6" s="106" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D6" s="107" t="n">
-        <x:v>0.4</x:v>
-      </x:c>
-      <x:c r="E6" s="107" t="n">
-        <x:v>0.1333</x:v>
-      </x:c>
-      <x:c r="F6" s="107" t="n">
-        <x:v>0.4667</x:v>
-      </x:c>
-      <x:c r="G6" s="108" t="n">
-        <x:v>0.500514</x:v>
-      </x:c>
-      <x:c r="H6" s="106" t="str">
-        <x:v>Negative</x:v>
-      </x:c>
-      <x:c r="I6" s="106" t="str">
-        <x:v>https://www.bilibili.com</x:v>
-      </x:c>
-      <x:c r="J6" s="106" t="str">
-        <x:v>https://www.xiaoheihe.cn</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="106" t="str">
-        <x:v>Cyberpunk Collaboration</x:v>
-      </x:c>
-      <x:c r="B7" s="106" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C7" s="106" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D7" s="107" t="n">
-        <x:v>0.3</x:v>
-      </x:c>
-      <x:c r="E7" s="107" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F7" s="107" t="n">
-        <x:v>0.7</x:v>
-      </x:c>
-      <x:c r="G7" s="108" t="n">
-        <x:v>0.333191</x:v>
-      </x:c>
-      <x:c r="H7" s="106" t="str">
-        <x:v>Negative</x:v>
-      </x:c>
-      <x:c r="I7" s="106" t="str">
-        <x:v>https://www.bilibili.com</x:v>
-      </x:c>
-      <x:c r="J7" s="106" t="str">
-        <x:v>https://www.xiaoheihe.cn</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="106" t="str">
-        <x:v>Creator Performance Interest</x:v>
-      </x:c>
-      <x:c r="B8" s="106" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C8" s="106" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D8" s="107" t="n">
-        <x:v>0.5455</x:v>
-      </x:c>
-      <x:c r="E8" s="107" t="n">
-        <x:v>0.1818</x:v>
-      </x:c>
-      <x:c r="F8" s="107" t="n">
-        <x:v>0.2727</x:v>
-      </x:c>
-      <x:c r="G8" s="108" t="n">
-        <x:v>0.541131</x:v>
-      </x:c>
-      <x:c r="H8" s="106" t="str">
-        <x:v>Positive</x:v>
-      </x:c>
-      <x:c r="I8" s="106" t="str">
-        <x:v>https://www.bilibili.com</x:v>
-      </x:c>
-      <x:c r="J8" s="106" t="str">
-        <x:v>https://www.xiaoheihe.cn</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="106" t="str">
-        <x:v>Cosmetic Experience Friction</x:v>
-      </x:c>
-      <x:c r="B9" s="106" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C9" s="106" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D9" s="107" t="n">
-        <x:v>0.5714</x:v>
-      </x:c>
-      <x:c r="E9" s="107" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F9" s="107" t="n">
-        <x:v>0.4286</x:v>
-      </x:c>
-      <x:c r="G9" s="108" t="n">
-        <x:v>0.628618</x:v>
-      </x:c>
-      <x:c r="H9" s="106" t="str">
-        <x:v>Positive</x:v>
-      </x:c>
-      <x:c r="I9" s="106" t="str">
-        <x:v>https://www.bilibili.com</x:v>
-      </x:c>
-      <x:c r="J9" s="106" t="str">
-        <x:v>https://www.xiaoheihe.cn</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="106" t="str">
-        <x:v>Ranked Version Discussion</x:v>
-      </x:c>
-      <x:c r="B10" s="106" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C10" s="106" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D10" s="107" t="n">
-        <x:v>0.7143</x:v>
-      </x:c>
-      <x:c r="E10" s="107" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F10" s="107" t="n">
-        <x:v>0.2857</x:v>
-      </x:c>
-      <x:c r="G10" s="108" t="n">
-        <x:v>0.645608</x:v>
-      </x:c>
-      <x:c r="H10" s="106" t="str">
-        <x:v>Positive</x:v>
-      </x:c>
-      <x:c r="I10" s="106" t="str">
-        <x:v>https://www.bilibili.com</x:v>
-      </x:c>
-      <x:c r="J10" s="106" t="str">
-        <x:v>https://www.xiaoheihe.cn</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="106" t="str">
-        <x:v>Legend Ability Balance</x:v>
-      </x:c>
-      <x:c r="B11" s="106" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C11" s="106" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D11" s="107" t="n">
-        <x:v>0.2857</x:v>
-      </x:c>
-      <x:c r="E11" s="107" t="n">
-        <x:v>0.2857</x:v>
-      </x:c>
-      <x:c r="F11" s="107" t="n">
-        <x:v>0.4286</x:v>
-      </x:c>
-      <x:c r="G11" s="108" t="n">
-        <x:v>0.482304</x:v>
-      </x:c>
-      <x:c r="H11" s="106" t="str">
-        <x:v>Negative</x:v>
-      </x:c>
-      <x:c r="I11" s="106" t="str">
-        <x:v>https://www.bilibili.com</x:v>
-      </x:c>
-      <x:c r="J11" s="106" t="str">
-        <x:v>https://www.xiaoheihe.cn</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="106" t="str">
-        <x:v>Mobility Strength Debate</x:v>
-      </x:c>
-      <x:c r="B12" s="106" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C12" s="106" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D12" s="107" t="n">
-        <x:v>0.4286</x:v>
-      </x:c>
-      <x:c r="E12" s="107" t="n">
-        <x:v>0.4286</x:v>
-      </x:c>
-      <x:c r="F12" s="107" t="n">
-        <x:v>0.1429</x:v>
-      </x:c>
-      <x:c r="G12" s="108" t="n">
-        <x:v>0.593134</x:v>
-      </x:c>
-      <x:c r="H12" s="106" t="str">
-        <x:v>Neutral</x:v>
-      </x:c>
-      <x:c r="I12" s="106" t="str">
-        <x:v>https://www.bilibili.com</x:v>
-      </x:c>
-      <x:c r="J12" s="106" t="str">
-        <x:v>https://www.xiaoheihe.cn</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13">
-      <x:c r="A13" s="106" t="str">
-        <x:v>Settings Help Requests</x:v>
-      </x:c>
-      <x:c r="B13" s="106" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C13" s="106" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D13" s="107" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E13" s="107" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F13" s="107" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="108" t="n">
-        <x:v>0.51082</x:v>
-      </x:c>
-      <x:c r="H13" s="106" t="str">
-        <x:v>Neutral</x:v>
-      </x:c>
-      <x:c r="I13" s="106" t="str">
-        <x:v>https://www.bilibili.com</x:v>
-      </x:c>
-      <x:c r="J13" s="106" t="str">
-        <x:v>https://www.xiaoheihe.cn</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14" s="109" t="str">
-        <x:v>Tournament Fairness Debate</x:v>
-      </x:c>
-      <x:c r="B14" s="109" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C14" s="109" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D14" s="110" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E14" s="110" t="n">
-        <x:v>0.3333</x:v>
-      </x:c>
-      <x:c r="F14" s="110" t="n">
-        <x:v>0.6667000000000001</x:v>
-      </x:c>
-      <x:c r="G14" s="111" t="n">
-        <x:v>0.276911</x:v>
-      </x:c>
-      <x:c r="H14" s="109" t="str">
-        <x:v>Negative</x:v>
-      </x:c>
-      <x:c r="I14" s="109" t="str">
-        <x:v>https://www.bilibili.com</x:v>
-      </x:c>
-      <x:c r="J14" s="109" t="str">
-        <x:v>https://www.xiaoheihe.cn</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15">
-      <x:c r="A15" s="112"/>
-      <x:c r="B15" s="112"/>
-      <x:c r="C15" s="112"/>
-      <x:c r="D15" s="112"/>
-      <x:c r="E15" s="112"/>
-      <x:c r="F15" s="112"/>
-      <x:c r="G15" s="112"/>
-      <x:c r="H15" s="112"/>
-      <x:c r="I15" s="112"/>
-      <x:c r="J15" s="112"/>
-    </x:row>
-    <x:row r="16">
-      <x:c r="A16" s="113" t="str">
-        <x:v>Top 10 mapped totals</x:v>
-      </x:c>
-      <x:c r="B16" s="114" t="n">
-        <x:f>SUM(B5:B14)</x:f>
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="C16" s="114" t="n">
-        <x:f>SUM(C5:C14)</x:f>
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D16" s="114"/>
-      <x:c r="E16" s="114" t="str">
-        <x:v>Weighted negative rate</x:v>
-      </x:c>
-      <x:c r="F16" s="115" t="n">
-        <x:f>SUMPRODUCT(B5:B14,F5:F14)/SUM(B5:B14)</x:f>
-        <x:v>0.4105368421052632</x:v>
-      </x:c>
-      <x:c r="G16" s="112"/>
-      <x:c r="H16" s="112"/>
-      <x:c r="I16" s="112"/>
-      <x:c r="J16" s="112"/>
-    </x:row>
-    <x:row r="17">
-      <x:c r="A17" s="112"/>
-      <x:c r="B17" s="112"/>
-      <x:c r="C17" s="112"/>
-      <x:c r="D17" s="112"/>
-      <x:c r="E17" s="112"/>
-      <x:c r="F17" s="112"/>
-      <x:c r="G17" s="112"/>
-      <x:c r="H17" s="112"/>
-      <x:c r="I17" s="112"/>
-      <x:c r="J17" s="112"/>
-    </x:row>
-    <x:row r="18">
-      <x:c r="A18" s="100" t="str">
-        <x:v>Quality field</x:v>
-      </x:c>
-      <x:c r="B18" s="102" t="str">
-        <x:v>Value</x:v>
-      </x:c>
-      <x:c r="C18" s="112"/>
-      <x:c r="D18" s="100" t="str">
-        <x:v>Provenance field</x:v>
-      </x:c>
-      <x:c r="E18" s="102" t="str">
-        <x:v>Value</x:v>
-      </x:c>
-      <x:c r="F18" s="112"/>
-      <x:c r="G18" s="112"/>
-      <x:c r="H18" s="112"/>
-      <x:c r="I18" s="112"/>
-      <x:c r="J18" s="112"/>
-    </x:row>
-    <x:row r="19">
-      <x:c r="A19" s="116" t="str">
-        <x:v>Bilibili raw rows</x:v>
-      </x:c>
-      <x:c r="B19" s="116" t="n">
-        <x:v>186</x:v>
-      </x:c>
-      <x:c r="C19" s="112"/>
-      <x:c r="D19" s="116" t="str">
-        <x:v>Bilibili raw SHA-256</x:v>
-      </x:c>
-      <x:c r="E19" s="116" t="str">
-        <x:v>32e040c1d251ae2085610df92f14277e384e69b8d56d8eb0ac775ae0dc3314ad</x:v>
-      </x:c>
-      <x:c r="F19" s="112"/>
-      <x:c r="G19" s="112"/>
-      <x:c r="H19" s="112"/>
-      <x:c r="I19" s="112"/>
-      <x:c r="J19" s="112"/>
-    </x:row>
-    <x:row r="20">
-      <x:c r="A20" s="117" t="str">
-        <x:v>Bilibili mapped rows</x:v>
-      </x:c>
-      <x:c r="B20" s="117" t="n">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="C20" s="112"/>
-      <x:c r="D20" s="117" t="str">
-        <x:v>Heybox raw SHA-256</x:v>
-      </x:c>
-      <x:c r="E20" s="117" t="str">
-        <x:v>13c85e8bf5bbd8316180dc46a3407f672ef9ea5bbfcb65cbbb1798d4baca9a59</x:v>
-      </x:c>
-      <x:c r="F20" s="112"/>
-      <x:c r="G20" s="112"/>
-      <x:c r="H20" s="112"/>
-      <x:c r="I20" s="112"/>
-      <x:c r="J20" s="112"/>
-    </x:row>
-    <x:row r="21">
-      <x:c r="A21" s="117" t="str">
-        <x:v>Bilibili outliers</x:v>
-      </x:c>
-      <x:c r="B21" s="117" t="n">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C21" s="112"/>
-      <x:c r="D21" s="117" t="str">
-        <x:v>Frozen model SHA-256</x:v>
-      </x:c>
-      <x:c r="E21" s="117" t="str">
-        <x:v>40f0c48d7dee49f2c3f804b3a5a896828c671503708a30f84be5812fc7e463a5</x:v>
-      </x:c>
-      <x:c r="F21" s="112"/>
-      <x:c r="G21" s="112"/>
-      <x:c r="H21" s="112"/>
-      <x:c r="I21" s="112"/>
-      <x:c r="J21" s="112"/>
-    </x:row>
-    <x:row r="22">
-      <x:c r="A22" s="117" t="str">
-        <x:v>Bilibili low confidence</x:v>
-      </x:c>
-      <x:c r="B22" s="117" t="n">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="C22" s="112"/>
-      <x:c r="D22" s="117" t="str">
-        <x:v>Confidence</x:v>
-      </x:c>
-      <x:c r="E22" s="117" t="str">
-        <x:v>HDBSCAN membership probability; topic -1 is 0.0</x:v>
-      </x:c>
-      <x:c r="F22" s="112"/>
-      <x:c r="G22" s="112"/>
-      <x:c r="H22" s="112"/>
-      <x:c r="I22" s="112"/>
-      <x:c r="J22" s="112"/>
-    </x:row>
-    <x:row r="23">
-      <x:c r="A23" s="117" t="str">
-        <x:v>Bilibili possible misclassification</x:v>
-      </x:c>
-      <x:c r="B23" s="117" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C23" s="112"/>
-      <x:c r="D23" s="117" t="str">
-        <x:v>Heybox scope</x:v>
-      </x:c>
-      <x:c r="E23" s="117" t="str">
-        <x:v>Public-search-visible post cards; no comment bodies</x:v>
-      </x:c>
-      <x:c r="F23" s="112"/>
-      <x:c r="G23" s="112"/>
-      <x:c r="H23" s="112"/>
-      <x:c r="I23" s="112"/>
-      <x:c r="J23" s="112"/>
-    </x:row>
-    <x:row r="24">
-      <x:c r="A24" s="117" t="str">
-        <x:v>Heybox raw rows</x:v>
-      </x:c>
-      <x:c r="B24" s="117" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C24" s="112"/>
-      <x:c r="D24" s="117" t="str">
-        <x:v>Formal reporting</x:v>
-      </x:c>
-      <x:c r="E24" s="117" t="str">
-        <x:v>Not qualified</x:v>
-      </x:c>
-      <x:c r="F24" s="112"/>
-      <x:c r="G24" s="112"/>
-      <x:c r="H24" s="112"/>
-      <x:c r="I24" s="112"/>
-      <x:c r="J24" s="112"/>
-    </x:row>
-    <x:row r="25">
-      <x:c r="A25" s="118" t="str">
-        <x:v>Heybox mapped rows</x:v>
-      </x:c>
-      <x:c r="B25" s="118" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C25" s="112"/>
-      <x:c r="D25" s="118" t="str">
-        <x:v>Combined units</x:v>
-      </x:c>
-      <x:c r="E25" s="118" t="str">
-        <x:v>Incomparable; exploratory view only</x:v>
-      </x:c>
-      <x:c r="F25" s="112"/>
-      <x:c r="G25" s="112"/>
-      <x:c r="H25" s="112"/>
-      <x:c r="I25" s="112"/>
-      <x:c r="J25" s="112"/>
-    </x:row>
-  </x:sheetData>
-  <x:mergeCells>
-    <x:mergeCell ref="A1:J1"/>
-    <x:mergeCell ref="A2:J2"/>
-  </x:mergeCells>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1dcb969fbb2646e7"/>
 </x:worksheet>
 </file>